--- a/AAII_Financials/Quarterly/SWK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SWK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>SWK</t>
   </si>
@@ -656,538 +656,550 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E7" s="2">
         <v>46116</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46025</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44562</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44198</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3960700</v>
+      </c>
+      <c r="E8" s="3">
         <v>3846400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3684600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3756000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3945200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3744600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3720500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3751300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4024400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3869500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3736500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3953900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4158900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3931800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3986800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4119600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4393000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4448000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3981900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3779700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3798900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3720800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13057700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3850200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3147400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3129400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3714200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3633100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3761300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3333600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3634700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3494800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3643600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3209300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3464200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3359400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3286700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2856300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2920400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2882000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2626400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2683900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2457300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2568400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2858100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2612500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2561700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2606300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2850000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2746800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2486100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2909500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3174800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3023000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3208800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3104000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3169300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3053800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2826700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2559000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2435800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2328600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8590600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2466900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2091700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2097300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2535600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2388600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2450500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2221000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2422800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2253400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2347500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2041600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4375300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4132900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4038700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1783300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1843800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1797900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1334300</v>
+      </c>
+      <c r="E10" s="3">
         <v>1162500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1227300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1187600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1087100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1132100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1158800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1145000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1174400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1122700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1250400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1044400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>984100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>908800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>778000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1015600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1223700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1394200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1155200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1220700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1363100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1392200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4467100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1383300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1055700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1032100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1178600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1244500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1310800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1112600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1211900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1241400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1296100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1167700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-911100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>-773500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>-752000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1073000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1076600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1084100</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1230,19 +1242,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>321400</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1250,11 +1263,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>328800</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1262,11 +1275,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>362000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1352,8 +1365,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1474,175 +1490,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-223300</v>
+      </c>
+      <c r="E14" s="3">
         <v>82700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>58300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>218100</v>
       </c>
-      <c r="G14" s="3">
-        <v>58000</v>
-      </c>
       <c r="H14" s="3">
+        <v>95700</v>
+      </c>
+      <c r="I14" s="3">
         <v>34200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>53700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>111700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>240800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>70800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>331700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>147300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>82300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>115200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>54000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>118700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>248100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>221400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>172400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>32500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>33200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>23800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>326200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>88800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>168900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>61900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>164000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>113000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>29300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>54700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>161200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>96800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>136200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>46900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>49600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>55400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>48900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-178400</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>21700</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>129400</v>
+      </c>
+      <c r="E15" s="3">
         <v>113000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>123700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>130200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>130100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>128400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>90700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>154700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>155000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>140200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>99300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>151100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>164400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>144200</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1718,8 +1740,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1759,252 +1784,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3626300</v>
+      </c>
+      <c r="E17" s="3">
         <v>3598800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3309300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3416400</v>
       </c>
-      <c r="G17" s="3">
-        <v>3729700</v>
-      </c>
       <c r="H17" s="3">
+        <v>3740200</v>
+      </c>
+      <c r="I17" s="3">
         <v>3497600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3473200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3474400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3732900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3648600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3392700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3762300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4041000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3876200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4055100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4047600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4305400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4217600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3857100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3367100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3259700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3102900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11632800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3329900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2981500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2921200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3420000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3280700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3293700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3083300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3416700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3130600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3293600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2927200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3084400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2972000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2882900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2356300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2595600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2509200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>334400</v>
+      </c>
+      <c r="E18" s="3">
         <v>247600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>375300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>339600</v>
       </c>
-      <c r="G18" s="3">
-        <v>215500</v>
-      </c>
       <c r="H18" s="3">
+        <v>205000</v>
+      </c>
+      <c r="I18" s="3">
         <v>247000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>247300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>276900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>291500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>220900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>343800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>191600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>117900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>55600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-68300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>72000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>87600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>230400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>124800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>412600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>539200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>617900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1424900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>520300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>165900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>208200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>294200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>352400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>467600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>250300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>218000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>364200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>350000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>282100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>379800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>387400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>403800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>500000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>324800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>372800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2047,618 +2079,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6800</v>
       </c>
-      <c r="G20" s="3">
-        <v>50600</v>
-      </c>
       <c r="H20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I20" s="3">
         <v>8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>13400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>30000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>15400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>70000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>17500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>14700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>8500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>18900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>26600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>12800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>13400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>32900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>20000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>24200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>10500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>24700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>6800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>464400</v>
+      </c>
+      <c r="E21" s="3">
         <v>356400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>491400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>463000</v>
       </c>
-      <c r="G21" s="3">
-        <v>295000</v>
-      </c>
       <c r="H21" s="3">
+        <v>332700</v>
+      </c>
+      <c r="I21" s="3">
         <v>367400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>344400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>434500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>452100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>347200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>439800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>335800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>270300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>186400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>108800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>225400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>237500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>376900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>341300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>559000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>684300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>764800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2020500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>667600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>313100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>347000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>441700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>508000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>617800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>407000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>370100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>506700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>491100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>438600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>522500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>532300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>530100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>626200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>434400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>481000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E22" s="3">
         <v>113100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>131700</v>
-      </c>
-      <c r="F22" s="3">
-        <v>129100</v>
       </c>
       <c r="G22" s="3">
         <v>129100</v>
       </c>
       <c r="H22" s="3">
+        <v>129100</v>
+      </c>
+      <c r="I22" s="3">
         <v>126400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>114400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>131400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>121300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>131500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>139300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>144600</v>
       </c>
       <c r="O22" s="3">
         <v>144600</v>
       </c>
       <c r="P22" s="3">
+        <v>144600</v>
+      </c>
+      <c r="Q22" s="3">
         <v>130900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>113900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>91700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>78200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>54700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>45800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>45600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>46500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>47500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>222600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>52700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>57300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>59700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>65100</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>72400</v>
       </c>
       <c r="AE22" s="3">
         <v>72400</v>
       </c>
       <c r="AF22" s="3">
+        <v>72400</v>
+      </c>
+      <c r="AG22" s="3">
         <v>74400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>73600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>72100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>69000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>63200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>58100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>57200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>56000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>51300</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>49300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>499000</v>
+      </c>
+      <c r="E23" s="3">
         <v>84800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>228000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>35600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>26700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>127600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>125400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>89500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>48300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-78800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-57000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-75800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-164100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-152200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>15900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>178500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>149000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>369200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>495400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>573300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1219800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>469600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>111100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>146200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>236800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>294700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>403700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>194800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>171000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>304900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>294400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>251800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>341700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>354400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>358300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>473400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>282300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>327700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>147700</v>
+      </c>
+      <c r="E24" s="3">
         <v>25200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>69800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-15800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-75200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>37200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-69500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>197300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-61700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-253300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-51600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-40900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-62800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>22900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-127200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>67300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>115500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>43000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>78400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-117300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>25300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>59200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>51600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>24700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>100500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>56600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>58600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>37000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>79900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>80700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>79700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>26500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>78700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2779,252 +2827,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>351300</v>
+      </c>
+      <c r="E26" s="3">
         <v>59600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>158200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>51400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>101900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>90400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>194900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>91100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-276100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>177500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-187800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>36600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>78700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>155600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>276200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>369700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>428100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>457800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1176800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>391200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>228400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>133300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>211500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>235500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>352100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>170100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>70500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>248300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>293400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>193200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>304700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>274500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>277600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>393700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>255800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>249000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>351300</v>
+      </c>
+      <c r="E27" s="3">
         <v>59600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>158200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>51400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>101900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>90400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>194900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>91100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-304400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>177000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-187800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-106200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>36900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>79000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>155800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>279600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>380000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>429000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>451000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1162600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>385500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>233700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>133200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>199100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>230500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>356300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>169900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>69700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>247800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>193700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>305100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>274500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>277600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>393700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>255500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>248900</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3145,8 +3202,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3172,52 +3232,52 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>8000</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-28300</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-500</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>55600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>808000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>9000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>19800</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>48900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>34600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>26000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>27200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>48800</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3237,23 +3297,23 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-176500</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-23100</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-23600</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3261,14 +3321,17 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3389,8 +3452,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3511,252 +3577,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6800</v>
       </c>
-      <c r="G32" s="3">
-        <v>-50600</v>
-      </c>
       <c r="H32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-30000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-15400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-70000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-17500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-18900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-26600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-12800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-13400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-32900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-24200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-24700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-6800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>351300</v>
+      </c>
+      <c r="E33" s="3">
         <v>59600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>158200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>51400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>101900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>90400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>194900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>91100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-304400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>177000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-187800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-50600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>844900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>88000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>175600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>328500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>414600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>455000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>478200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1211400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>385500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>233700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>133200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>199100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>230500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>356300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>169900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-106800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>247800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>170600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>281500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>274500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>277600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>393700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>255500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>248900</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3877,257 +3952,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>351300</v>
+      </c>
+      <c r="E35" s="3">
         <v>59600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>158200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>51400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>101900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>90400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>194900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>91100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-304400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>177000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-187800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-50600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>844900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>88000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>175600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>328500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>414600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>455000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>478200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1211400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>385500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>233700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>133200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>199100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>230500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>356300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>169900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-106800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>247800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>170600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>281500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>274500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>277600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>393700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>255500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>248900</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E38" s="2">
         <v>46116</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46025</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44562</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44198</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4170,8 +4254,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4214,130 +4299,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>592400</v>
+      </c>
+      <c r="E41" s="3">
         <v>333700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>280100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>268300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>311800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>344800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>290500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>298700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>318500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>476600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>449400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>347800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>391400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>387600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>395600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>408700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>282300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>165800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>142300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>292700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>440400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>949200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1381000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>683000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>859800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>987100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>297700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>311700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>310700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>281800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>288700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>368700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>385800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>405600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>637500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>483300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>539500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>378000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1131800</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>420800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4458,496 +4547,511 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1471000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1438400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>919700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1419600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1542400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1566000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1153700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1503100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1512100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1708900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1302000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1623300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1706700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1607900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1231000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1503200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1592100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1842000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1560800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1989000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1994700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1994800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1512200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1764200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1719400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1681500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1454600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1902600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1823900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1882100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1607800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2236200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2151400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1986100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1628700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2009800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1927900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1728000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1302800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1730200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3896500</v>
+      </c>
+      <c r="E44" s="3">
         <v>4059000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4157100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4442600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4639000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4707100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4536400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4630000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4562400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4693300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4738600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4977700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5282900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5659500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5861100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6347200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6635500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6267700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5446800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4134400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3679500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3137400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2737400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2874700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2753400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2532400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2255000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2743500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2863200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2791600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2373500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2649700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2444200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2350300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2018400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2247400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2078000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1976700</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1478000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1720300</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E45" s="3">
         <v>305000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>286200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>47700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>155300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>162200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>487000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>545500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1462900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1460700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1376500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>460300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>441100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>441600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>405400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>465100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>436900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>491900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>449300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>370200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>347400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>298400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>299400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>300800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>341200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>335900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>509000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>288200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>293700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>285600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>875900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>390800</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6343700</v>
+      </c>
+      <c r="E46" s="3">
         <v>6506800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5979000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6500600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6877800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7009100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6377700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6830900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6785000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7420800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7017300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7379100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7839700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8135700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7974700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8804600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9972800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9736200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8526400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6876400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6555700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6523000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6036000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5787000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5769500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5692900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4456600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5328000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5345200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5253900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4569400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5555400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5322600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5077900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4559000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5028700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4839100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4368300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4788500</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4262100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4990,8 +5094,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5008,26 +5112,26 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>140900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>139900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>135900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>135000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>138900</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
@@ -5035,8 +5139,8 @@
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG47" s="3">
         <v>0</v>
@@ -5068,252 +5172,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2151000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2218000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2296100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2393700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2474000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2469100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2507700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2558300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2578900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2605300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2672800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2714400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2756000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2748400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2784600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2708300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2709100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2785700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2780400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2512900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2515900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2511300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2576600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2531700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2540400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2559200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1959500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1911900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1933300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1927400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1915200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1846200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1817100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1770200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1742500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1677300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1649800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1538300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1451200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1480100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10289400</v>
+      </c>
+      <c r="E49" s="3">
         <v>10325300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10374800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11557500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11735000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11649200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11636400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11791500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11801700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11857800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11945500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12669100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12890300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12946800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12977500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>12860900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13031800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>13237300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>13483700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>13837000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>13934700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>13965200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>14093500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>13956000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>13911600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>13877400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>12859500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>12813000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>12954900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>13028300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>12441100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>12554100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>12544400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>12325100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>15790900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>12240800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>12020200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>11967500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>8993500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>9589300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5434,8 +5547,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5556,130 +5672,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1309400</v>
+      </c>
+      <c r="E52" s="3">
         <v>2549700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2593800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1302100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1405800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1368800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1327100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1301100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1288600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1970000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2028200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1334500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1447200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1240800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1226500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1150100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3647700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3599500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3389500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1100300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>956600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>735600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>720300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>630300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>627900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>636600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1321000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1269600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1290200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1250700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>482300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>492000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>495500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>510000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>512700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>826400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>803200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>788000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>401700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>389200</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5800,130 +5922,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20093500</v>
+      </c>
+      <c r="E54" s="3">
         <v>21599800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21243700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21753900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>22492600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22496200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21848900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22481800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22454200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23853900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23663800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24097100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24933200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25071700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>24963300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25523900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29361400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>29358700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>28180000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24326600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23962900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23876000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23566300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23040900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>22984400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>22905000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>20596600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>21322500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>21523600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>21460300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>19408000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>20447700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>20179600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>19683200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>19097700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>19773200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>19312300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>18662100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>15634900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>15720700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5966,8 +6094,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6010,740 +6139,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2422300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2220100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>2163000</v>
       </c>
       <c r="F57" s="3">
         <v>2163000</v>
       </c>
       <c r="G57" s="3">
+        <v>2163000</v>
+      </c>
+      <c r="H57" s="3">
         <v>2495400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2531600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2437200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2405200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2450400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2337500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2298900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2252600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2413900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2378700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2344400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2492800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3138800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3367700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3438900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3055700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2998700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2653200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2446400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2345300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2117400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2029200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2087800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2070300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2323800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2264300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2233200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2320200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2288500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2172700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2021000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2091600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2093000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1928800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1640400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1741200</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1797200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1293500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1909800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1919400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1984600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>627000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>887600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>992500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2240400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1203600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1501300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1785100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1830000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2104100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2570400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5834200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5087600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2242400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>152200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>6300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>706200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1216700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>583700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>555200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>885700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>378600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1455400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1155900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1069900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>988100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>114400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>134300</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>205700</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>12100</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>102200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E59" s="3">
         <v>119100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>392800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>32100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>63300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>422600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>27900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>53900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>858000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2120700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2543800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2787700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2499700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3086100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2372900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2401200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1924400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2110400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1870200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1754700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2124400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2313000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2787900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2774100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2616200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1389800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2276400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2194500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1567600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1387700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1796200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1639600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2079900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1155000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1619600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4429100</v>
+      </c>
+      <c r="E60" s="3">
         <v>5716600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5245700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5862500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6592100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6348700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4916900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5292300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5342800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6829400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5883200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5663300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6139600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6239300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6569200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7607000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11760700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10955000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8767400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5580800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5402500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4578400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4558300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4221800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4578300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5370300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4405700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5441900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5653100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5766200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4001600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6052000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5638900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4810200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4391500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4002200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3866900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4214400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2807500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>3463000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5157800</v>
+      </c>
+      <c r="E61" s="3">
         <v>5169300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5046900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5140800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5223900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5229900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5967800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6118300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6109700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6097000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6479900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6621300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6619300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6550400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5352900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5350500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5351800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5355500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4353600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4246900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4246200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4245700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4245400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4658500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4658700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4662600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3176400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3908800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3909100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3909400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3819800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2830600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2831200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2827600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2828200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3818000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3817400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3815600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3815300</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3815100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1178100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1367400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1440900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1394700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1172200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1607600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1682800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1648200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1682200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1389500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1447900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1685400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1701700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1720200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3327000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3017700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3167000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3693400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3466600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3180700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3228200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3647100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3696200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3781300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3781800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3912900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3872300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3703600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3728100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3848000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3746700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3480000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3521700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3603600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3573000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3934200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3921600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3814000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2638500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2361400</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6864,8 +7012,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6986,8 +7137,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7108,130 +7262,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11134700</v>
+      </c>
+      <c r="E66" s="3">
         <v>12623100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12189100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12776600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13429600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13654600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13129000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13622600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13732300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14977500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14607700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14767700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15397300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15579300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15251200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15977300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20281600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20005900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16589500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13010300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12878900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>12474200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12506700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12668000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13024900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13951600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11460300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13060200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13295600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13527800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11571800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12365500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>11994200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>11244000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>10795500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>11757500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>11612300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>11850600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>9267900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>9686200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7274,8 +7434,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7396,8 +7557,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7518,8 +7682,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7566,7 +7733,7 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
-        <v>620300</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3">
         <v>620300</v>
@@ -7578,13 +7745,13 @@
         <v>620300</v>
       </c>
       <c r="V70" s="3">
-        <v>750000</v>
+        <v>620300</v>
       </c>
       <c r="W70" s="3">
         <v>750000</v>
       </c>
       <c r="X70" s="3">
-        <v>1500000</v>
+        <v>750000</v>
       </c>
       <c r="Y70" s="3">
         <v>1500000</v>
@@ -7602,7 +7769,7 @@
         <v>1500000</v>
       </c>
       <c r="AD70" s="3">
-        <v>750000</v>
+        <v>1500000</v>
       </c>
       <c r="AE70" s="3">
         <v>750000</v>
@@ -7632,7 +7799,7 @@
         <v>750000</v>
       </c>
       <c r="AN70" s="3">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="AO70" s="3">
         <v>0</v>
@@ -7640,8 +7807,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7762,130 +7932,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8405200</v>
+      </c>
+      <c r="E72" s="3">
         <v>8178200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8244600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8212700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8287100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8309200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8343300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8272400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8304900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8437900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8540200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8966400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9083000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9025700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9333300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9504100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8775000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8801400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8742400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8546800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8258600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7915500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7547600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7200400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6924500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6796600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6772800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6678100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6549900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6291300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6219000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6424300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6273900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6074500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5998700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5803900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5624400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5433800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>5127300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4958700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8006,8 +8182,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8128,8 +8307,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8250,130 +8432,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8958800</v>
+      </c>
+      <c r="E76" s="3">
         <v>8976700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9054600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8977300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9063000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8841600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8719900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8859200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8721900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8876400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9056100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9327300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9533800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9490300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9712100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8926300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8459500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8732500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10970200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10566300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10334000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9901800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9559600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8872900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8459500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7453400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7636300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7512300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7478000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7182500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7086200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7332200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7435400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7689200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7552200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>7265700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6950000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6811500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6367000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6034500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8494,257 +8682,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E80" s="2">
         <v>46116</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46025</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44562</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44198</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>351300</v>
+      </c>
+      <c r="E81" s="3">
         <v>59600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>158200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>51400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>101900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>90400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>194900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>91100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-304400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>177000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-187800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-50600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>844900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>88000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>175600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>328500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>414600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>455000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>478200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1211400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>385500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>233700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>133200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>199100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>230500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>356300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>169900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-106800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>247800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>170600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>281500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>274500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>277600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>393700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>255500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>248900</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8787,130 +8984,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>92700</v>
+      </c>
+      <c r="E83" s="3">
         <v>91100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>50100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>113900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>114300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>99100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>51300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>103000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>116100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>95900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>97000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>88400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>91900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>92000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>147100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>138000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>143400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>143700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>146500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>144200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>142400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>144000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>578100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>145300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>144700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>141100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>139800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>140900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>141700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>137800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>125500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>129700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>127700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>123600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>122700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>120700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>115800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>101500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>102800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>103100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9031,8 +9232,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9153,8 +9357,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9275,8 +9482,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9397,8 +9607,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9519,130 +9732,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>763100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-388800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>955700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>221200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>214300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-420000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>679100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>285800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>573000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-431000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>769300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>443900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>264400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-286300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>651100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-425600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-443900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1241100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>371900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>444400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-157800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2022100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>677200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>328200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-405200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1243300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>192700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>501000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-431300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1220800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>191500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>198000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-349400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>950800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>356900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>256500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-145600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>835200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>246700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9685,130 +9904,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-58500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-72800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-65900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-79600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-65000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-114500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-86500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-87200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-65700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-122300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-79900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-68300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-68200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-130500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-114400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-145700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-139800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-196600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-129100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-105100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-88300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-348100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-62100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-64500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-82900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-141200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-96700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-97200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-89600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-164700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-109400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-111700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-106300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-164500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-122200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-129400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-125300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-78100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9929,8 +10152,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10051,130 +10277,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1753200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-55500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-71500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-65100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-67200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-106600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-85400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>649400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-63200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-120900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-76400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-69200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-61200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-124600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>4014900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-154300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-163400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2224100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-143000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-108800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-147900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1577100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-63800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-56800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1363700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-68700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-100400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-32200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1007300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-140900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-134400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-587500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-126300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>107800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-32200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-46400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1596000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-61300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10217,34 +10449,35 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>124300</v>
+      </c>
+      <c r="E96" s="3">
         <v>126000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>126300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>125800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>124000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>124500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>124000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>123600</v>
-      </c>
-      <c r="K96" s="3">
-        <v>121800</v>
       </c>
       <c r="L96" s="3">
         <v>121800</v>
@@ -10253,94 +10486,97 @@
         <v>121800</v>
       </c>
       <c r="N96" s="3">
+        <v>121800</v>
+      </c>
+      <c r="O96" s="3">
         <v>121300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>119700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>119800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-120000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-115500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-114000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-116300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-127100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-126000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-111600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-110100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-431800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-109600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-105800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-105600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-104400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-102300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-97700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-97600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-98400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-97400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-94200</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-94900</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-95000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-94700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-86500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-86700</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-87000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-84500</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10461,8 +10697,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10583,8 +10822,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10705,370 +10947,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2251100</v>
+      </c>
+      <c r="E100" s="3">
         <v>508200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-885300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-188100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-223000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>502000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-502900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-234300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1368100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>548600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-576700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-387700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-175800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>324200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-600100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3404600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>608200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1425400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1859200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>7800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-853300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-95000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>615900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-810200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-391500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2475200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1203400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-67400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-429900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1408200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1137400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-97600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>457500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>215900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-650700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-161900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>35000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1072800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>13700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-325400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E101" s="3">
         <v>31500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-77700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>14100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-15000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-27600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>30800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-23600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-14200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>9100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>63900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-78200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-22400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>63900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-78200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-22400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-15600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-15500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-38900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>22800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>16300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-22600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>19000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-25400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>5800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-87800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>27900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>22300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>21100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>38100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-78900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>259600</v>
+      </c>
+      <c r="E102" s="3">
         <v>57000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-37800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-33300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>55800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-19800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-160700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>26800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>102500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-43800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>106500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>25700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-146100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-509200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-439600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1083700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-180500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-121700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>683700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>39100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-25600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-57300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-34700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-19800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-231900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>154200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-56200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>161500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-753800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>711000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-147400</v>
       </c>
     </row>
